--- a/public/templates/restaurant-import-template.xlsx
+++ b/public/templates/restaurant-import-template.xlsx
@@ -397,117 +397,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:I2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>순서</v>
+      </c>
+      <c r="B1" t="str">
         <v>상호명</v>
       </c>
-      <c r="B1" t="str">
-        <v>상호명(영문)</v>
-      </c>
       <c r="C1" t="str">
+        <v>주소</v>
+      </c>
+      <c r="D1" t="str">
+        <v>전화번호</v>
+      </c>
+      <c r="E1" t="str">
+        <v>영업시간</v>
+      </c>
+      <c r="F1" t="str">
+        <v>휴무일</v>
+      </c>
+      <c r="G1" t="str">
         <v>카테고리</v>
       </c>
-      <c r="D1" t="str">
-        <v>2차분류</v>
-      </c>
-      <c r="E1" t="str">
-        <v>주소</v>
-      </c>
-      <c r="F1" t="str">
-        <v>키오스크숨김</v>
-      </c>
-      <c r="G1" t="str">
-        <v>전화</v>
-      </c>
       <c r="H1" t="str">
-        <v>홈페이지</v>
+        <v>주요메뉴</v>
       </c>
       <c r="I1" t="str">
-        <v>오픈시간</v>
-      </c>
-      <c r="J1" t="str">
-        <v>마감시간</v>
-      </c>
-      <c r="K1" t="str">
-        <v>도보(분)</v>
-      </c>
-      <c r="L1" t="str">
-        <v>태그</v>
-      </c>
-      <c r="M1" t="str">
-        <v>소개(한)</v>
-      </c>
-      <c r="N1" t="str">
-        <v>소개(영)</v>
-      </c>
-      <c r="O1" t="str">
-        <v>이미지URL</v>
-      </c>
-      <c r="P1" t="str">
-        <v>약도URL</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>메뉴URL</v>
+        <v>한줄설명</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
         <v>예시맛집</v>
       </c>
-      <c r="B2" t="str">
-        <v>Sample Restaurant</v>
-      </c>
       <c r="C2" t="str">
+        <v>지하1층 푸드코트</v>
+      </c>
+      <c r="D2" t="str">
+        <v>02-123-4567</v>
+      </c>
+      <c r="E2" t="str">
+        <v>11:00-21:00</v>
+      </c>
+      <c r="F2" t="str">
+        <v>매주 월요일</v>
+      </c>
+      <c r="G2" t="str">
         <v>korean</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>지하1층 푸드코트</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="str">
-        <v>02-123-4567</v>
-      </c>
       <c r="H2" t="str">
-        <v/>
+        <v>비빔밥·갈비</v>
       </c>
       <c r="I2" t="str">
-        <v>11:00</v>
-      </c>
-      <c r="J2" t="str">
-        <v>21:00</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2" t="str">
-        <v>주차,룸</v>
-      </c>
-      <c r="M2" t="str">
         <v>한식 전문점입니다.</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Korean restaurant.</v>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>